--- a/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92994142089</v>
+        <v>46157.9308175192</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9308175192</v>
+        <v>46157.93352576326</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93352576326</v>
+        <v>46157.9364022989</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9364022989</v>
+        <v>46158.28177748522</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28177748522</v>
+        <v>46158.29754292833</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46157.92959867477</v>
+        <v>46158.29717824768</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>45674.79292512169</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>46157.92959867477</v>
+        <v>46158.29717824768</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29754292833</v>
+        <v>46158.29772354185</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29772354185</v>
+        <v>46158.30446414935</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.30446414935</v>
+        <v>46158.3334123244</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3334123244</v>
+        <v>46158.37201983991</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/04_Соглашения/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37201983991</v>
+        <v>46158.37417581875</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -724,7 +724,7 @@
         <v>6.8</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46158.29717824768</v>
+        <v>46158.37373759849</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>45674.79292512169</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>46158.29717824768</v>
+        <v>46158.37373759849</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
